--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -8362,7 +8362,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -8413,7 +8413,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8209,7 +8209,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -501,11 +501,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -603,11 +603,11 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -654,11 +654,11 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -756,11 +756,11 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -811,12 +811,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -858,11 +858,11 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2366,11 +2366,11 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2417,11 +2417,11 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2468,11 +2468,11 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2519,11 +2519,11 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2570,11 +2570,11 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2621,11 +2621,11 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2672,11 +2672,11 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2723,11 +2723,11 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2774,11 +2774,11 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2825,11 +2825,11 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2876,11 +2876,11 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2927,11 +2927,11 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2978,11 +2978,11 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3029,11 +3029,11 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3080,11 +3080,11 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3131,11 +3131,11 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3182,11 +3182,11 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3233,11 +3233,11 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
+          <t>2022-09-30</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3339,12 +3339,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3390,12 +3390,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4257,12 +4257,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4308,12 +4308,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4359,12 +4359,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -7954,11 +7954,11 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8005,11 +8005,11 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8056,11 +8056,11 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8158,11 +8158,11 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -8209,11 +8209,11 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -8311,11 +8311,11 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -8362,11 +8362,11 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -8413,11 +8413,11 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8158,7 +8158,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -8311,7 +8311,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4712,7 +4712,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5120,7 +5120,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5273,7 +5273,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -6781,7 +6781,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -6934,7 +6934,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -6985,7 +6985,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7036,7 +7036,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7138,7 +7138,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7189,7 +7189,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -7240,7 +7240,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -7444,7 +7444,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -7750,7 +7750,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -7801,7 +7801,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -8362,7 +8362,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -8413,7 +8413,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2978,7 +2978,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8209,7 +8209,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">

--- a/data/final/documentacao/lista_dashboards.xlsx
+++ b/data/final/documentacao/lista_dashboards.xlsx
@@ -705,11 +705,11 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -756,11 +756,11 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -807,11 +807,11 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -858,11 +858,11 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3284,11 +3284,11 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3335,11 +3335,11 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3386,11 +3386,11 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3437,11 +3437,11 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3488,11 +3488,11 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3539,11 +3539,11 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3590,11 +3590,11 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3641,11 +3641,11 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3692,11 +3692,11 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3743,11 +3743,11 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3794,11 +3794,11 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3845,11 +3845,11 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3896,11 +3896,11 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3947,11 +3947,11 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3998,11 +3998,11 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4049,11 +4049,11 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4100,11 +4100,11 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4151,11 +4151,11 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4202,11 +4202,11 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4253,11 +4253,11 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4304,11 +4304,11 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4355,11 +4355,11 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4406,11 +4406,11 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4457,11 +4457,11 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4508,11 +4508,11 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4559,11 +4559,11 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4610,11 +4610,11 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4661,11 +4661,11 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7954,11 +7954,11 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8005,11 +8005,11 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8158,11 +8158,11 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2021-11-30</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -8311,11 +8311,11 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>2021-11-30</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
